--- a/laporan_padel_dki_jakarta_2026-10-02.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-02.xlsx
@@ -3943,16 +3943,16 @@
         <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>21.4%</t>
+          <t>22.9%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp2.473.000</t>
+          <t>Rp2.648.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -4532,16 +4532,16 @@
         <v>90</v>
       </c>
       <c r="D33" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>21.1%</t>
+          <t>18.9%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp3.675.000</t>
+          <t>Rp3.225.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4625,16 +4625,16 @@
         <v>28</v>
       </c>
       <c r="D36" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp378.000</t>
+          <t>Rp0</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -5245,16 +5245,16 @@
         <v>75</v>
       </c>
       <c r="D56" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rp124.000</t>
+          <t>Rp177.000</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -6040,16 +6040,16 @@
         <v>36</v>
       </c>
       <c r="D11" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>52.8%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp3.962.000</t>
+          <t>Rp4.322.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -6195,16 +6195,16 @@
         <v>102</v>
       </c>
       <c r="D16" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp5.225.000</t>
+          <t>Rp5.500.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7362,16 +7362,16 @@
         <v>187</v>
       </c>
       <c r="D33" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>42.2%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp13.350.000</t>
+          <t>Rp13.400.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-10-02.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-02.xlsx
@@ -606,16 +606,16 @@
         <v>34</v>
       </c>
       <c r="D6" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>20.6%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp1.500.000</t>
+          <t>Rp1.650.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1009,16 +1009,16 @@
         <v>108</v>
       </c>
       <c r="D19" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>15.7%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp2.720.000</t>
+          <t>Rp2.895.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1226,16 +1226,16 @@
         <v>68</v>
       </c>
       <c r="D26" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>14.7%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp1.850.000</t>
+          <t>Rp1.625.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1319,16 +1319,16 @@
         <v>16</v>
       </c>
       <c r="D29" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>68.8%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp1.439.000</t>
+          <t>Rp1.564.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1381,16 +1381,16 @@
         <v>68</v>
       </c>
       <c r="D31" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>44.1%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp3.310.000</t>
+          <t>Rp3.409.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2249,16 +2249,16 @@
         <v>32</v>
       </c>
       <c r="D59" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rp1.350.000</t>
+          <t>Rp1.625.000</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -2311,16 +2311,16 @@
         <v>112</v>
       </c>
       <c r="D61" t="n">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>4.5%</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rp1.096.000</t>
+          <t>Rp896.000</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -2435,16 +2435,16 @@
         <v>34</v>
       </c>
       <c r="D65" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rp840.000</t>
+          <t>Rp900.000</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -2776,16 +2776,16 @@
         <v>98</v>
       </c>
       <c r="D76" t="n">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>8.2%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Rp1.490.000</t>
+          <t>Rp2.230.000</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -2838,16 +2838,16 @@
         <v>120</v>
       </c>
       <c r="D78" t="n">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rp8.160.000</t>
+          <t>Rp7.215.000</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -2869,16 +2869,16 @@
         <v>108</v>
       </c>
       <c r="D79" t="n">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Rp2.325.000</t>
+          <t>Rp2.675.000</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -3055,16 +3055,16 @@
         <v>135</v>
       </c>
       <c r="D85" t="n">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>16.3%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Rp4.620.000</t>
+          <t>Rp5.070.000</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -3179,16 +3179,16 @@
         <v>138</v>
       </c>
       <c r="D89" t="n">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>23.2%</t>
+          <t>24.6%</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Rp5.650.000</t>
+          <t>Rp5.950.000</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -3365,16 +3365,16 @@
         <v>34</v>
       </c>
       <c r="D95" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Rp1.525.000</t>
+          <t>Rp1.650.000</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -3489,16 +3489,16 @@
         <v>28</v>
       </c>
       <c r="D99" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>32.1%</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Rp1.765.000</t>
+          <t>Rp2.425.000</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -3602,16 +3602,16 @@
         <v>127</v>
       </c>
       <c r="D3" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>55.1%</t>
+          <t>55.9%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp16.479.000</t>
+          <t>Rp16.714.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -3633,16 +3633,16 @@
         <v>102</v>
       </c>
       <c r="D4" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>19.6%</t>
+          <t>21.6%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp7.156.000</t>
+          <t>Rp7.934.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -3912,16 +3912,16 @@
         <v>57</v>
       </c>
       <c r="D13" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>21.1%</t>
+          <t>17.5%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp3.475.000</t>
+          <t>Rp3.100.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -4284,16 +4284,16 @@
         <v>63</v>
       </c>
       <c r="D25" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>17.5%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp2.525.000</t>
+          <t>Rp3.025.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -4315,16 +4315,16 @@
         <v>17</v>
       </c>
       <c r="D26" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp230.000</t>
+          <t>Rp310.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -4377,16 +4377,16 @@
         <v>180</v>
       </c>
       <c r="D28" t="n">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp17.690.000</t>
+          <t>Rp17.115.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4532,16 +4532,16 @@
         <v>90</v>
       </c>
       <c r="D33" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>18.9%</t>
+          <t>14.4%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp3.225.000</t>
+          <t>Rp2.475.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4594,16 +4594,16 @@
         <v>70</v>
       </c>
       <c r="D35" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>25.7%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp3.260.000</t>
+          <t>Rp3.900.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -4656,16 +4656,16 @@
         <v>159</v>
       </c>
       <c r="D37" t="n">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>34.0%</t>
+          <t>35.2%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp17.250.000</t>
+          <t>Rp18.000.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -4749,16 +4749,16 @@
         <v>54</v>
       </c>
       <c r="D40" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>20.4%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp1.910.000</t>
+          <t>Rp2.035.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -4997,16 +4997,16 @@
         <v>80</v>
       </c>
       <c r="D48" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>38.8%</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rp4.750.000</t>
+          <t>Rp4.875.000</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -5090,16 +5090,16 @@
         <v>54</v>
       </c>
       <c r="D51" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rp6.000.000</t>
+          <t>Rp6.800.000</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -5121,16 +5121,16 @@
         <v>60</v>
       </c>
       <c r="D52" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>36.7%</t>
+          <t>38.3%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rp7.200.000</t>
+          <t>Rp7.450.000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -5245,16 +5245,16 @@
         <v>75</v>
       </c>
       <c r="D56" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>6.7%</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rp177.000</t>
+          <t>Rp283.000</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -5555,16 +5555,16 @@
         <v>144</v>
       </c>
       <c r="D66" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>28.5%</t>
+          <t>29.2%</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rp16.600.000</t>
+          <t>Rp17.050.000</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -5947,16 +5947,16 @@
         <v>272</v>
       </c>
       <c r="D8" t="n">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>25.4%</t>
+          <t>25.7%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp33.150.000</t>
+          <t>Rp33.550.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -5978,16 +5978,16 @@
         <v>54</v>
       </c>
       <c r="D9" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>24.1%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp2.425.000</t>
+          <t>Rp2.825.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -6009,16 +6009,16 @@
         <v>72</v>
       </c>
       <c r="D10" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp7.365.000</t>
+          <t>Rp8.265.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -6288,16 +6288,16 @@
         <v>15</v>
       </c>
       <c r="D19" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp168.000</t>
+          <t>Rp336.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -6401,16 +6401,16 @@
         <v>186</v>
       </c>
       <c r="D2" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>30.1%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp12.370.000</t>
+          <t>Rp12.550.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -6525,16 +6525,16 @@
         <v>216</v>
       </c>
       <c r="D6" t="n">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>24.5%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp11.070.000</t>
+          <t>Rp11.220.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -6711,16 +6711,16 @@
         <v>54</v>
       </c>
       <c r="D12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>35.2%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp1.900.000</t>
+          <t>Rp1.800.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -6835,16 +6835,16 @@
         <v>108</v>
       </c>
       <c r="D16" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>21.3%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp4.225.000</t>
+          <t>Rp4.575.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6875,12 +6875,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp3.475.000</t>
+          <t>Rp3.733.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Rp50.000 - Rp275.000</t>
+          <t>Rp44.000 - Rp275.000</t>
         </is>
       </c>
     </row>
@@ -7114,16 +7114,16 @@
         <v>108</v>
       </c>
       <c r="D25" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp6.741.000</t>
+          <t>Rp6.940.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -7176,16 +7176,16 @@
         <v>96</v>
       </c>
       <c r="D27" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>39.6%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp7.650.000</t>
+          <t>Rp7.800.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -7269,16 +7269,16 @@
         <v>80</v>
       </c>
       <c r="D30" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>32.5%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp3.825.000</t>
+          <t>Rp4.000.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -7331,16 +7331,16 @@
         <v>108</v>
       </c>
       <c r="D32" t="n">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>37.0%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp7.970.000</t>
+          <t>Rp8.850.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -7362,16 +7362,16 @@
         <v>187</v>
       </c>
       <c r="D33" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>42.2%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp13.400.000</t>
+          <t>Rp13.250.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -7548,16 +7548,16 @@
         <v>150</v>
       </c>
       <c r="D39" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>60.7%</t>
+          <t>61.3%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp28.175.000</t>
+          <t>Rp28.475.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -7796,16 +7796,16 @@
         <v>108</v>
       </c>
       <c r="D47" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rp1.650.000</t>
+          <t>Rp2.200.000</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -7858,16 +7858,16 @@
         <v>144</v>
       </c>
       <c r="D49" t="n">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp3.050.000</t>
+          <t>Rp3.400.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -7971,16 +7971,16 @@
         <v>76</v>
       </c>
       <c r="D2" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>15.8%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp2.200.000</t>
+          <t>Rp2.400.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -8002,16 +8002,16 @@
         <v>136</v>
       </c>
       <c r="D3" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>44.9%</t>
+          <t>45.6%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp11.030.000</t>
+          <t>Rp11.110.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -8033,16 +8033,16 @@
         <v>34</v>
       </c>
       <c r="D4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp2.200.000</t>
+          <t>Rp2.440.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -8064,16 +8064,16 @@
         <v>88</v>
       </c>
       <c r="D5" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>11.4%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp2.500.000</t>
+          <t>Rp3.100.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -8157,16 +8157,16 @@
         <v>51</v>
       </c>
       <c r="D8" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>19.6%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp2.080.000</t>
+          <t>Rp1.710.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -8219,16 +8219,16 @@
         <v>90</v>
       </c>
       <c r="D10" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>42.2%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp7.185.000</t>
+          <t>Rp7.800.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -8281,16 +8281,16 @@
         <v>72</v>
       </c>
       <c r="D12" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp6.870.000</t>
+          <t>Rp7.320.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -8374,16 +8374,16 @@
         <v>54</v>
       </c>
       <c r="D15" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp3.974.992</t>
+          <t>Rp4.099.992</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -8560,16 +8560,16 @@
         <v>108</v>
       </c>
       <c r="D21" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>37.0%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp14.240.000</t>
+          <t>Rp13.840.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-10-02.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-02.xlsx
@@ -668,16 +668,16 @@
         <v>64</v>
       </c>
       <c r="D8" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>48.4%</t>
+          <t>45.3%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp5.440.000</t>
+          <t>Rp5.120.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -730,16 +730,16 @@
         <v>72</v>
       </c>
       <c r="D10" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>26.4%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp4.650.992</t>
+          <t>Rp5.179.990</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -761,16 +761,16 @@
         <v>126</v>
       </c>
       <c r="D11" t="n">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>15.1%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp5.100.000</t>
+          <t>Rp5.600.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -978,16 +978,16 @@
         <v>72</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp2.300.000</t>
+          <t>Rp2.500.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1009,16 +1009,16 @@
         <v>108</v>
       </c>
       <c r="D19" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>15.7%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp2.895.000</t>
+          <t>Rp3.170.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1071,16 +1071,16 @@
         <v>127</v>
       </c>
       <c r="D21" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>37.0%</t>
+          <t>37.8%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp13.090.000</t>
+          <t>Rp13.335.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1102,16 +1102,16 @@
         <v>168</v>
       </c>
       <c r="D22" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>25.6%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp13.494.000</t>
+          <t>Rp13.794.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1195,16 +1195,16 @@
         <v>64</v>
       </c>
       <c r="D25" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp1.850.000</t>
+          <t>Rp1.975.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1288,16 +1288,16 @@
         <v>36</v>
       </c>
       <c r="D28" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp596.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1381,16 +1381,16 @@
         <v>68</v>
       </c>
       <c r="D31" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>44.1%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp3.409.000</t>
+          <t>Rp3.159.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1443,16 +1443,16 @@
         <v>85</v>
       </c>
       <c r="D33" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp1.959.000</t>
+          <t>Rp2.057.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1567,16 +1567,16 @@
         <v>72</v>
       </c>
       <c r="D37" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>52.8%</t>
+          <t>51.4%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp5.725.000</t>
+          <t>Rp5.600.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -1598,16 +1598,16 @@
         <v>64</v>
       </c>
       <c r="D38" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp6.910.000</t>
+          <t>Rp7.080.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -1660,16 +1660,16 @@
         <v>72</v>
       </c>
       <c r="D40" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp840.000</t>
+          <t>Rp1.260.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -1970,16 +1970,16 @@
         <v>28</v>
       </c>
       <c r="D50" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rp310.000</t>
+          <t>Rp425.000</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -2218,16 +2218,16 @@
         <v>54</v>
       </c>
       <c r="D58" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rp525.000</t>
+          <t>Rp685.000</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -2311,16 +2311,16 @@
         <v>112</v>
       </c>
       <c r="D61" t="n">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>4.5%</t>
+          <t>8.0%</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rp896.000</t>
+          <t>Rp1.692.000</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -2373,16 +2373,16 @@
         <v>68</v>
       </c>
       <c r="D63" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>45.6%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rp4.510.000</t>
+          <t>Rp4.600.000</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -2404,16 +2404,16 @@
         <v>30</v>
       </c>
       <c r="D64" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rp590.000</t>
+          <t>Rp531.000</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -2497,16 +2497,16 @@
         <v>90</v>
       </c>
       <c r="D67" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rp2.589.000</t>
+          <t>Rp2.988.000</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -2652,16 +2652,16 @@
         <v>68</v>
       </c>
       <c r="D72" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>20.6%</t>
+          <t>22.1%</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rp2.400.000</t>
+          <t>Rp2.580.000</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -2683,16 +2683,16 @@
         <v>72</v>
       </c>
       <c r="D73" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rp1.055.000</t>
+          <t>Rp715.000</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -2714,16 +2714,16 @@
         <v>90</v>
       </c>
       <c r="D74" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Rp1.525.000</t>
+          <t>Rp2.175.000</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -2776,16 +2776,16 @@
         <v>98</v>
       </c>
       <c r="D76" t="n">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Rp2.230.000</t>
+          <t>Rp3.310.000</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -2869,16 +2869,16 @@
         <v>108</v>
       </c>
       <c r="D79" t="n">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>28.7%</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Rp2.675.000</t>
+          <t>Rp2.975.000</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -2900,16 +2900,16 @@
         <v>114</v>
       </c>
       <c r="D80" t="n">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Rp850.000</t>
+          <t>Rp1.850.000</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -2931,16 +2931,16 @@
         <v>80</v>
       </c>
       <c r="D81" t="n">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>13.8%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Rp2.014.000</t>
+          <t>Rp3.010.000</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -3055,16 +3055,16 @@
         <v>135</v>
       </c>
       <c r="D85" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Rp5.070.000</t>
+          <t>Rp5.295.000</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -3086,16 +3086,16 @@
         <v>108</v>
       </c>
       <c r="D86" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>21.3%</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Rp5.500.000</t>
+          <t>Rp5.900.000</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -3179,16 +3179,16 @@
         <v>138</v>
       </c>
       <c r="D89" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>24.6%</t>
+          <t>26.1%</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Rp5.950.000</t>
+          <t>Rp6.275.000</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -3241,16 +3241,16 @@
         <v>119</v>
       </c>
       <c r="D91" t="n">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>26.9%</t>
+          <t>30.3%</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Rp5.045.000</t>
+          <t>Rp5.665.000</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -3427,16 +3427,16 @@
         <v>112</v>
       </c>
       <c r="D97" t="n">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>29.5%</t>
+          <t>32.1%</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Rp5.400.000</t>
+          <t>Rp5.970.000</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -3602,16 +3602,16 @@
         <v>127</v>
       </c>
       <c r="D3" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>55.9%</t>
+          <t>57.5%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp16.714.000</t>
+          <t>Rp17.284.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -3633,16 +3633,16 @@
         <v>102</v>
       </c>
       <c r="D4" t="n">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>21.6%</t>
+          <t>27.5%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp7.934.000</t>
+          <t>Rp10.190.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -3695,16 +3695,16 @@
         <v>85</v>
       </c>
       <c r="D6" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>1.2%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp180.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -3757,16 +3757,16 @@
         <v>36</v>
       </c>
       <c r="D8" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp5.650.000</t>
+          <t>Rp5.950.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3912,16 +3912,16 @@
         <v>57</v>
       </c>
       <c r="D13" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>17.5%</t>
+          <t>22.8%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp3.100.000</t>
+          <t>Rp4.300.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -4191,16 +4191,16 @@
         <v>34</v>
       </c>
       <c r="D22" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>44.1%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp2.580.000</t>
+          <t>Rp2.715.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -4253,16 +4253,16 @@
         <v>53</v>
       </c>
       <c r="D24" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>45.3%</t>
+          <t>47.2%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp12.700.000</t>
+          <t>Rp12.900.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -4377,16 +4377,16 @@
         <v>180</v>
       </c>
       <c r="D28" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>33.9%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp17.115.000</t>
+          <t>Rp17.390.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4842,16 +4842,16 @@
         <v>77</v>
       </c>
       <c r="D43" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>29.9%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp8.500.000</t>
+          <t>Rp8.750.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -4887,7 +4887,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Rp300.000</t>
+          <t>Rp250.000 - Rp300.000</t>
         </is>
       </c>
     </row>
@@ -5090,16 +5090,16 @@
         <v>54</v>
       </c>
       <c r="D51" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>53.7%</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rp6.800.000</t>
+          <t>Rp7.100.000</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -5121,16 +5121,16 @@
         <v>60</v>
       </c>
       <c r="D52" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>38.3%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rp7.450.000</t>
+          <t>Rp8.900.000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -5183,16 +5183,16 @@
         <v>68</v>
       </c>
       <c r="D54" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>36.8%</t>
+          <t>39.7%</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rp7.425.000</t>
+          <t>Rp7.975.000</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -5245,16 +5245,16 @@
         <v>75</v>
       </c>
       <c r="D56" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rp283.000</t>
+          <t>Rp416.000</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -5431,16 +5431,16 @@
         <v>64</v>
       </c>
       <c r="D62" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>14.1%</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rp4.800.000</t>
+          <t>Rp5.400.000</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -5555,16 +5555,16 @@
         <v>144</v>
       </c>
       <c r="D66" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>29.2%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rp17.050.000</t>
+          <t>Rp18.250.000</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -5761,16 +5761,16 @@
         <v>18</v>
       </c>
       <c r="D2" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp480.000</t>
+          <t>Rp800.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -5885,16 +5885,16 @@
         <v>36</v>
       </c>
       <c r="D6" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp1.290.000</t>
+          <t>Rp1.415.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -5947,16 +5947,16 @@
         <v>272</v>
       </c>
       <c r="D8" t="n">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>25.7%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp33.550.000</t>
+          <t>Rp34.750.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -5978,16 +5978,16 @@
         <v>54</v>
       </c>
       <c r="D9" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>31.5%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp2.825.000</t>
+          <t>Rp3.525.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -6009,16 +6009,16 @@
         <v>72</v>
       </c>
       <c r="D10" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp8.265.000</t>
+          <t>Rp8.085.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -6133,16 +6133,16 @@
         <v>51</v>
       </c>
       <c r="D14" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>37.3%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp4.650.000</t>
+          <t>Rp4.825.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6164,16 +6164,16 @@
         <v>54</v>
       </c>
       <c r="D15" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp4.740.000</t>
+          <t>Rp4.890.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6195,16 +6195,16 @@
         <v>102</v>
       </c>
       <c r="D16" t="n">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp5.500.000</t>
+          <t>Rp6.325.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6226,16 +6226,16 @@
         <v>34</v>
       </c>
       <c r="D17" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>38.2%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp2.050.000</t>
+          <t>Rp2.450.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -6463,16 +6463,16 @@
         <v>79</v>
       </c>
       <c r="D4" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>54.4%</t>
+          <t>58.2%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp11.560.000</t>
+          <t>Rp12.290.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -6525,16 +6525,16 @@
         <v>216</v>
       </c>
       <c r="D6" t="n">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>24.5%</t>
+          <t>25.5%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp11.220.000</t>
+          <t>Rp11.620.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -6773,16 +6773,16 @@
         <v>144</v>
       </c>
       <c r="D14" t="n">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>48.6%</t>
+          <t>50.7%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp14.110.000</t>
+          <t>Rp14.685.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6875,7 +6875,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp3.733.000</t>
+          <t>Rp3.739.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7052,16 +7052,16 @@
         <v>112</v>
       </c>
       <c r="D23" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>41.1%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp9.842.000</t>
+          <t>Rp10.004.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -7269,16 +7269,16 @@
         <v>80</v>
       </c>
       <c r="D30" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>32.5%</t>
+          <t>27.5%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp4.000.000</t>
+          <t>Rp3.500.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -7300,16 +7300,16 @@
         <v>72</v>
       </c>
       <c r="D31" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>15.3%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp2.755.000</t>
+          <t>Rp1.615.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -7331,16 +7331,16 @@
         <v>108</v>
       </c>
       <c r="D32" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>37.0%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp8.850.000</t>
+          <t>Rp9.290.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -7362,16 +7362,16 @@
         <v>187</v>
       </c>
       <c r="D33" t="n">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>43.3%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp13.250.000</t>
+          <t>Rp13.150.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -7517,16 +7517,16 @@
         <v>14</v>
       </c>
       <c r="D38" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>64.3%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp1.225.000</t>
+          <t>Rp1.575.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -7548,16 +7548,16 @@
         <v>150</v>
       </c>
       <c r="D39" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>61.3%</t>
+          <t>62.0%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp28.475.000</t>
+          <t>Rp28.700.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -7672,16 +7672,16 @@
         <v>112</v>
       </c>
       <c r="D43" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>47.3%</t>
+          <t>48.2%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp11.555.000</t>
+          <t>Rp11.730.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -7796,16 +7796,16 @@
         <v>108</v>
       </c>
       <c r="D47" t="n">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rp2.200.000</t>
+          <t>Rp3.300.000</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -7858,16 +7858,16 @@
         <v>144</v>
       </c>
       <c r="D49" t="n">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp3.400.000</t>
+          <t>Rp3.650.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -7889,16 +7889,16 @@
         <v>90</v>
       </c>
       <c r="D50" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>6.7%</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rp800.000</t>
+          <t>Rp1.300.000</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -7971,16 +7971,16 @@
         <v>76</v>
       </c>
       <c r="D2" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>15.8%</t>
+          <t>18.4%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp2.400.000</t>
+          <t>Rp2.800.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -8064,16 +8064,16 @@
         <v>88</v>
       </c>
       <c r="D5" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>11.4%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp3.100.000</t>
+          <t>Rp2.500.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -8095,16 +8095,16 @@
         <v>72</v>
       </c>
       <c r="D6" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp6.726.000</t>
+          <t>Rp5.530.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -8250,16 +8250,16 @@
         <v>108</v>
       </c>
       <c r="D11" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp4.260.000</t>
+          <t>Rp4.590.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -8281,16 +8281,16 @@
         <v>72</v>
       </c>
       <c r="D12" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>43.1%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp7.320.000</t>
+          <t>Rp7.680.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -8374,16 +8374,16 @@
         <v>54</v>
       </c>
       <c r="D15" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>53.7%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp4.099.992</t>
+          <t>Rp4.224.992</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -8467,16 +8467,16 @@
         <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>53.7%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp7.090.000</t>
+          <t>Rp7.340.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -8529,16 +8529,16 @@
         <v>48</v>
       </c>
       <c r="D20" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>35.4%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp3.905.000</t>
+          <t>Rp4.005.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8560,16 +8560,16 @@
         <v>108</v>
       </c>
       <c r="D21" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>38.0%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp13.840.000</t>
+          <t>Rp14.700.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -8746,16 +8746,16 @@
         <v>54</v>
       </c>
       <c r="D27" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp4.135.000</t>
+          <t>Rp4.420.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -8808,16 +8808,16 @@
         <v>36</v>
       </c>
       <c r="D29" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp2.150.000</t>
+          <t>Rp3.100.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -8870,16 +8870,16 @@
         <v>54</v>
       </c>
       <c r="D31" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp2.625.000</t>
+          <t>Rp2.850.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -8963,16 +8963,16 @@
         <v>54</v>
       </c>
       <c r="D34" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp965.000</t>
+          <t>Rp1.530.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -9025,16 +9025,16 @@
         <v>144</v>
       </c>
       <c r="D36" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>21.5%</t>
+          <t>20.1%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp5.157.000</t>
+          <t>Rp4.957.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -9087,16 +9087,16 @@
         <v>72</v>
       </c>
       <c r="D38" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>48.6%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp3.171.000</t>
+          <t>Rp3.470.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -9118,16 +9118,16 @@
         <v>54</v>
       </c>
       <c r="D39" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp5.260.000</t>
+          <t>Rp5.810.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-10-02.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-02.xlsx
@@ -544,16 +544,16 @@
         <v>168</v>
       </c>
       <c r="D4" t="n">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>16.1%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp14.860.000</t>
+          <t>Rp13.960.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -575,16 +575,16 @@
         <v>80</v>
       </c>
       <c r="D5" t="n">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>21.2%</t>
+          <t>26.2%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp2.283.000</t>
+          <t>Rp3.079.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -637,16 +637,16 @@
         <v>64</v>
       </c>
       <c r="D7" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>14.1%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp898.000</t>
+          <t>Rp1.168.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -668,16 +668,16 @@
         <v>64</v>
       </c>
       <c r="D8" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>45.3%</t>
+          <t>48.4%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp5.120.000</t>
+          <t>Rp5.600.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -730,16 +730,16 @@
         <v>72</v>
       </c>
       <c r="D10" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp5.179.990</t>
+          <t>Rp6.035.989</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -761,16 +761,16 @@
         <v>126</v>
       </c>
       <c r="D11" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>17.5%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp5.600.000</t>
+          <t>Rp5.750.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -792,16 +792,16 @@
         <v>96</v>
       </c>
       <c r="D12" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp9.205.000</t>
+          <t>Rp8.705.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -823,16 +823,16 @@
         <v>51</v>
       </c>
       <c r="D13" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>31.4%</t>
+          <t>27.5%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp3.500.000</t>
+          <t>Rp3.100.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -854,16 +854,16 @@
         <v>180</v>
       </c>
       <c r="D14" t="n">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>21.1%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp8.839.000</t>
+          <t>Rp9.045.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -916,16 +916,16 @@
         <v>112</v>
       </c>
       <c r="D16" t="n">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>15.2%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp2.400.000</t>
+          <t>Rp2.720.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -978,16 +978,16 @@
         <v>72</v>
       </c>
       <c r="D18" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp2.500.000</t>
+          <t>Rp2.700.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1009,16 +1009,16 @@
         <v>108</v>
       </c>
       <c r="D19" t="n">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp3.170.000</t>
+          <t>Rp3.520.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1164,16 +1164,16 @@
         <v>144</v>
       </c>
       <c r="D24" t="n">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>26.4%</t>
+          <t>29.2%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp6.650.000</t>
+          <t>Rp7.450.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1195,16 +1195,16 @@
         <v>64</v>
       </c>
       <c r="D25" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp1.975.000</t>
+          <t>Rp2.475.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1226,16 +1226,16 @@
         <v>68</v>
       </c>
       <c r="D26" t="n">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp1.625.000</t>
+          <t>Rp575.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1257,16 +1257,16 @@
         <v>16</v>
       </c>
       <c r="D27" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp125.000</t>
+          <t>Rp525.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1288,16 +1288,16 @@
         <v>36</v>
       </c>
       <c r="D28" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp596.000</t>
+          <t>Rp1.392.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1319,16 +1319,16 @@
         <v>16</v>
       </c>
       <c r="D29" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>68.8%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp1.564.000</t>
+          <t>Rp1.376.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1350,16 +1350,16 @@
         <v>54</v>
       </c>
       <c r="D30" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp1.440.000</t>
+          <t>Rp2.400.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1412,16 +1412,16 @@
         <v>60</v>
       </c>
       <c r="D32" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>15.0%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp1.501.000</t>
+          <t>Rp1.213.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1536,16 +1536,16 @@
         <v>68</v>
       </c>
       <c r="D36" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>30.9%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp1.782.000</t>
+          <t>Rp2.079.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -1660,16 +1660,16 @@
         <v>72</v>
       </c>
       <c r="D40" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp1.260.000</t>
+          <t>Rp2.100.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -1691,16 +1691,16 @@
         <v>54</v>
       </c>
       <c r="D41" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp540.000</t>
+          <t>Rp1.125.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -1722,16 +1722,16 @@
         <v>51</v>
       </c>
       <c r="D42" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>31.4%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp2.180.000</t>
+          <t>Rp2.520.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -1750,24 +1750,24 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>180</v>
+        <v>198</v>
       </c>
       <c r="D43" t="n">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp7.050.000</t>
+          <t>Rp9.150.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Rp200.000 - Rp400.000</t>
+          <t>Rp100.000 - Rp400.000</t>
         </is>
       </c>
     </row>
@@ -1784,16 +1784,16 @@
         <v>198</v>
       </c>
       <c r="D44" t="n">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp2.975.000</t>
+          <t>Rp4.025.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -1815,16 +1815,16 @@
         <v>60</v>
       </c>
       <c r="D45" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rp2.100.000</t>
+          <t>Rp2.310.000</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -1877,16 +1877,16 @@
         <v>54</v>
       </c>
       <c r="D47" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rp420.000</t>
+          <t>Rp2.020.000</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -1939,16 +1939,16 @@
         <v>105</v>
       </c>
       <c r="D49" t="n">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>9.5%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp1.225.000</t>
+          <t>Rp1.925.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -2187,16 +2187,16 @@
         <v>48</v>
       </c>
       <c r="D57" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>27.1%</t>
+          <t>22.9%</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rp2.295.000</t>
+          <t>Rp1.895.000</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -2218,16 +2218,16 @@
         <v>54</v>
       </c>
       <c r="D58" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rp685.000</t>
+          <t>Rp845.000</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -2342,16 +2342,16 @@
         <v>90</v>
       </c>
       <c r="D62" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rp2.820.000</t>
+          <t>Rp3.420.000</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -2373,16 +2373,16 @@
         <v>68</v>
       </c>
       <c r="D63" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>52.9%</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rp4.600.000</t>
+          <t>Rp4.920.000</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -2497,16 +2497,16 @@
         <v>90</v>
       </c>
       <c r="D67" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rp2.988.000</t>
+          <t>Rp3.328.000</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -2559,16 +2559,16 @@
         <v>34</v>
       </c>
       <c r="D69" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>44.1%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rp1.485.000</t>
+          <t>Rp1.584.000</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -2590,16 +2590,16 @@
         <v>176</v>
       </c>
       <c r="D70" t="n">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>4.5%</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rp249.000</t>
+          <t>Rp1.992.000</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -2683,16 +2683,16 @@
         <v>72</v>
       </c>
       <c r="D73" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rp715.000</t>
+          <t>Rp885.000</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -2745,16 +2745,16 @@
         <v>96</v>
       </c>
       <c r="D75" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Rp2.860.000</t>
+          <t>Rp2.080.000</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -2931,16 +2931,16 @@
         <v>80</v>
       </c>
       <c r="D81" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>23.8%</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Rp3.010.000</t>
+          <t>Rp3.517.000</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -2962,16 +2962,16 @@
         <v>54</v>
       </c>
       <c r="D82" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>40.7%</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Rp1.982.000</t>
+          <t>Rp2.778.000</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -3055,16 +3055,16 @@
         <v>135</v>
       </c>
       <c r="D85" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Rp5.295.000</t>
+          <t>Rp5.070.000</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -3086,16 +3086,16 @@
         <v>108</v>
       </c>
       <c r="D86" t="n">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>21.3%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Rp5.900.000</t>
+          <t>Rp4.700.000</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -3117,16 +3117,16 @@
         <v>36</v>
       </c>
       <c r="D87" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Rp3.440.000</t>
+          <t>Rp2.300.000</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -3179,16 +3179,16 @@
         <v>138</v>
       </c>
       <c r="D89" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>26.1%</t>
+          <t>26.8%</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Rp6.275.000</t>
+          <t>Rp6.375.000</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -3241,16 +3241,16 @@
         <v>119</v>
       </c>
       <c r="D91" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>30.3%</t>
+          <t>31.1%</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Rp5.665.000</t>
+          <t>Rp5.845.000</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -3272,16 +3272,16 @@
         <v>36</v>
       </c>
       <c r="D92" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp650.000</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -3365,16 +3365,16 @@
         <v>34</v>
       </c>
       <c r="D95" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Rp1.650.000</t>
+          <t>Rp1.875.000</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -3427,16 +3427,16 @@
         <v>112</v>
       </c>
       <c r="D97" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>32.1%</t>
+          <t>33.9%</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Rp5.970.000</t>
+          <t>Rp6.370.000</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -3458,16 +3458,16 @@
         <v>68</v>
       </c>
       <c r="D98" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>1.5%</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Rp225.000</t>
+          <t>Rp675.000</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -3633,16 +3633,16 @@
         <v>102</v>
       </c>
       <c r="D4" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>27.5%</t>
+          <t>25.5%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp10.190.000</t>
+          <t>Rp9.412.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -3726,16 +3726,16 @@
         <v>162</v>
       </c>
       <c r="D7" t="n">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>29.0%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp7.460.000</t>
+          <t>Rp7.810.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3912,16 +3912,16 @@
         <v>57</v>
       </c>
       <c r="D13" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>22.8%</t>
+          <t>24.6%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp4.300.000</t>
+          <t>Rp5.050.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -4005,16 +4005,16 @@
         <v>105</v>
       </c>
       <c r="D16" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>21.0%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp9.200.000</t>
+          <t>Rp7.850.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -4036,16 +4036,16 @@
         <v>65</v>
       </c>
       <c r="D17" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>24.6%</t>
+          <t>26.2%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp6.840.000</t>
+          <t>Rp7.245.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -4067,16 +4067,16 @@
         <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>35.2%</t>
+          <t>42.6%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp4.350.000</t>
+          <t>Rp5.550.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -4191,16 +4191,16 @@
         <v>34</v>
       </c>
       <c r="D22" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>44.1%</t>
+          <t>52.9%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp2.715.000</t>
+          <t>Rp3.300.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -4253,16 +4253,16 @@
         <v>53</v>
       </c>
       <c r="D24" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>47.2%</t>
+          <t>49.1%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp12.900.000</t>
+          <t>Rp13.100.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -4284,16 +4284,16 @@
         <v>63</v>
       </c>
       <c r="D25" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>17.5%</t>
+          <t>19.0%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp3.025.000</t>
+          <t>Rp3.410.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -4377,16 +4377,16 @@
         <v>180</v>
       </c>
       <c r="D28" t="n">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>33.9%</t>
+          <t>35.6%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp17.390.000</t>
+          <t>Rp18.300.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4532,16 +4532,16 @@
         <v>90</v>
       </c>
       <c r="D33" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp2.475.000</t>
+          <t>Rp2.925.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4594,16 +4594,16 @@
         <v>70</v>
       </c>
       <c r="D35" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>25.7%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp3.900.000</t>
+          <t>Rp4.400.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -4625,16 +4625,16 @@
         <v>28</v>
       </c>
       <c r="D36" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp378.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -4656,16 +4656,16 @@
         <v>159</v>
       </c>
       <c r="D37" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>35.2%</t>
+          <t>35.8%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp18.000.000</t>
+          <t>Rp18.600.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -4718,16 +4718,16 @@
         <v>32</v>
       </c>
       <c r="D39" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>28.1%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp2.700.000</t>
+          <t>Rp4.700.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -4873,16 +4873,16 @@
         <v>54</v>
       </c>
       <c r="D44" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp250.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -4935,16 +4935,16 @@
         <v>6</v>
       </c>
       <c r="D46" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rp2.700.000</t>
+          <t>Rp4.200.000</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -4997,16 +4997,16 @@
         <v>80</v>
       </c>
       <c r="D48" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>38.8%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rp4.875.000</t>
+          <t>Rp5.325.000</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -5028,16 +5028,16 @@
         <v>90</v>
       </c>
       <c r="D49" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>35.6%</t>
+          <t>36.7%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp5.650.000</t>
+          <t>Rp5.875.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -5245,16 +5245,16 @@
         <v>75</v>
       </c>
       <c r="D56" t="n">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rp416.000</t>
+          <t>Rp867.000</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -5493,16 +5493,16 @@
         <v>102</v>
       </c>
       <c r="D64" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>24.5%</t>
+          <t>25.5%</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rp7.290.000</t>
+          <t>Rp7.587.000</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -5524,16 +5524,16 @@
         <v>84</v>
       </c>
       <c r="D65" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>27.4%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rp7.840.000</t>
+          <t>Rp7.140.000</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -5586,16 +5586,16 @@
         <v>30</v>
       </c>
       <c r="D67" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>56.7%</t>
+          <t>70.0%</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rp2.325.000</t>
+          <t>Rp2.875.000</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -5854,16 +5854,16 @@
         <v>108</v>
       </c>
       <c r="D5" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>28.7%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp9.450.000</t>
+          <t>Rp9.800.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -5885,16 +5885,16 @@
         <v>36</v>
       </c>
       <c r="D6" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp1.415.000</t>
+          <t>Rp2.475.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -5916,16 +5916,16 @@
         <v>68</v>
       </c>
       <c r="D7" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>38.2%</t>
+          <t>39.7%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp2.820.000</t>
+          <t>Rp2.920.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -5947,16 +5947,16 @@
         <v>272</v>
       </c>
       <c r="D8" t="n">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>27.6%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp34.750.000</t>
+          <t>Rp36.550.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -5978,16 +5978,16 @@
         <v>54</v>
       </c>
       <c r="D9" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>31.5%</t>
+          <t>35.2%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp3.525.000</t>
+          <t>Rp4.225.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -6009,16 +6009,16 @@
         <v>72</v>
       </c>
       <c r="D10" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>40.3%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp8.085.000</t>
+          <t>Rp7.285.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -6040,16 +6040,16 @@
         <v>36</v>
       </c>
       <c r="D11" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp4.322.000</t>
+          <t>Rp5.091.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -6133,16 +6133,16 @@
         <v>51</v>
       </c>
       <c r="D14" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>37.3%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp4.825.000</t>
+          <t>Rp4.225.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6164,16 +6164,16 @@
         <v>54</v>
       </c>
       <c r="D15" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp4.890.000</t>
+          <t>Rp5.460.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6195,16 +6195,16 @@
         <v>102</v>
       </c>
       <c r="D16" t="n">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>19.6%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp6.325.000</t>
+          <t>Rp6.650.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6257,16 +6257,16 @@
         <v>48</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp1.600.000</t>
+          <t>Rp2.000.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -6288,16 +6288,16 @@
         <v>15</v>
       </c>
       <c r="D19" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp336.000</t>
+          <t>Rp792.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -6319,16 +6319,16 @@
         <v>64</v>
       </c>
       <c r="D20" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp2.994.000</t>
+          <t>Rp3.493.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -6410,7 +6410,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp12.550.000</t>
+          <t>Rp13.190.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -6432,16 +6432,16 @@
         <v>101</v>
       </c>
       <c r="D3" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>15.8%</t>
+          <t>14.9%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp11.700.000</t>
+          <t>Rp11.450.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -6494,16 +6494,16 @@
         <v>90</v>
       </c>
       <c r="D5" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp597.000</t>
+          <t>Rp666.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6525,16 +6525,16 @@
         <v>216</v>
       </c>
       <c r="D6" t="n">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>25.5%</t>
+          <t>26.9%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp11.620.000</t>
+          <t>Rp12.245.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -6556,16 +6556,16 @@
         <v>144</v>
       </c>
       <c r="D7" t="n">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>16.0%</t>
+          <t>21.5%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp7.175.000</t>
+          <t>Rp9.625.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -6587,16 +6587,16 @@
         <v>54</v>
       </c>
       <c r="D8" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp2.200.000</t>
+          <t>Rp3.125.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -6618,16 +6618,16 @@
         <v>108</v>
       </c>
       <c r="D9" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>34.3%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp7.884.000</t>
+          <t>Rp8.120.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -6711,16 +6711,16 @@
         <v>54</v>
       </c>
       <c r="D12" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>37.0%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp1.800.000</t>
+          <t>Rp2.000.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -6742,16 +6742,16 @@
         <v>42</v>
       </c>
       <c r="D13" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>38.1%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp4.488.000</t>
+          <t>Rp5.604.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -6773,16 +6773,16 @@
         <v>144</v>
       </c>
       <c r="D14" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>50.7%</t>
+          <t>52.8%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp14.685.000</t>
+          <t>Rp15.510.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6990,16 +6990,16 @@
         <v>153</v>
       </c>
       <c r="D21" t="n">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>40.5%</t>
+          <t>47.7%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp20.600.000</t>
+          <t>Rp23.400.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -7052,16 +7052,16 @@
         <v>112</v>
       </c>
       <c r="D23" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>41.1%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp10.004.000</t>
+          <t>Rp8.210.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -7176,16 +7176,16 @@
         <v>96</v>
       </c>
       <c r="D27" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>39.6%</t>
+          <t>40.6%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp7.800.000</t>
+          <t>Rp8.050.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -7207,16 +7207,16 @@
         <v>68</v>
       </c>
       <c r="D28" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>20.6%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp2.760.000</t>
+          <t>Rp4.140.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -7269,16 +7269,16 @@
         <v>80</v>
       </c>
       <c r="D30" t="n">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>27.5%</t>
+          <t>33.8%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp3.500.000</t>
+          <t>Rp4.325.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -7362,16 +7362,16 @@
         <v>187</v>
       </c>
       <c r="D33" t="n">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>43.3%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp13.150.000</t>
+          <t>Rp16.250.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -7455,16 +7455,16 @@
         <v>85</v>
       </c>
       <c r="D36" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp3.375.000</t>
+          <t>Rp3.725.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -7579,16 +7579,16 @@
         <v>112</v>
       </c>
       <c r="D40" t="n">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>17.0%</t>
+          <t>20.5%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp7.499.000</t>
+          <t>Rp9.099.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -7765,16 +7765,16 @@
         <v>36</v>
       </c>
       <c r="D46" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rp4.280.000</t>
+          <t>Rp4.780.000</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -7827,16 +7827,16 @@
         <v>98</v>
       </c>
       <c r="D48" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>40.8%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rp9.040.000</t>
+          <t>Rp9.720.000</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -7889,16 +7889,16 @@
         <v>90</v>
       </c>
       <c r="D50" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>8.9%</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rp1.300.000</t>
+          <t>Rp1.900.000</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -8002,16 +8002,16 @@
         <v>136</v>
       </c>
       <c r="D3" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>45.6%</t>
+          <t>44.9%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp11.110.000</t>
+          <t>Rp10.750.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -8033,16 +8033,16 @@
         <v>34</v>
       </c>
       <c r="D4" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp2.440.000</t>
+          <t>Rp2.960.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -8064,16 +8064,16 @@
         <v>88</v>
       </c>
       <c r="D5" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>11.4%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp2.500.000</t>
+          <t>Rp3.200.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -8157,16 +8157,16 @@
         <v>51</v>
       </c>
       <c r="D8" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>19.6%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp1.710.000</t>
+          <t>Rp2.080.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -8219,16 +8219,16 @@
         <v>90</v>
       </c>
       <c r="D10" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>42.2%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp7.800.000</t>
+          <t>Rp7.500.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -8281,16 +8281,16 @@
         <v>72</v>
       </c>
       <c r="D12" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>43.1%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp7.680.000</t>
+          <t>Rp8.080.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -8374,16 +8374,16 @@
         <v>54</v>
       </c>
       <c r="D15" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>53.7%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp4.224.992</t>
+          <t>Rp4.474.992</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -8405,16 +8405,16 @@
         <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp1.850.000</t>
+          <t>Rp2.850.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -8436,16 +8436,16 @@
         <v>54</v>
       </c>
       <c r="D17" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>20.4%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp792.000</t>
+          <t>Rp1.089.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -8498,16 +8498,16 @@
         <v>54</v>
       </c>
       <c r="D19" t="n">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>20.4%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp1.140.000</t>
+          <t>Rp2.090.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8529,16 +8529,16 @@
         <v>48</v>
       </c>
       <c r="D20" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>35.4%</t>
+          <t>47.9%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp4.005.000</t>
+          <t>Rp5.645.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8560,16 +8560,16 @@
         <v>108</v>
       </c>
       <c r="D21" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>38.0%</t>
+          <t>37.0%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp14.700.000</t>
+          <t>Rp14.220.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -8591,16 +8591,16 @@
         <v>17</v>
       </c>
       <c r="D22" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp320.000</t>
+          <t>Rp480.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -8653,16 +8653,16 @@
         <v>144</v>
       </c>
       <c r="D24" t="n">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp3.870.000</t>
+          <t>Rp4.650.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -8684,16 +8684,16 @@
         <v>36</v>
       </c>
       <c r="D25" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp1.215.000</t>
+          <t>Rp2.011.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -8808,16 +8808,16 @@
         <v>36</v>
       </c>
       <c r="D29" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp3.100.000</t>
+          <t>Rp3.600.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -8870,16 +8870,16 @@
         <v>54</v>
       </c>
       <c r="D31" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp2.850.000</t>
+          <t>Rp3.075.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -9118,16 +9118,16 @@
         <v>54</v>
       </c>
       <c r="D39" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>42.6%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp5.810.000</t>
+          <t>Rp4.560.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -9149,16 +9149,16 @@
         <v>64</v>
       </c>
       <c r="D40" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp838.000</t>
+          <t>Rp1.176.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -9211,16 +9211,16 @@
         <v>68</v>
       </c>
       <c r="D42" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp998.000</t>
+          <t>Rp1.993.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-10-02.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-02.xlsx
@@ -482,16 +482,16 @@
         <v>108</v>
       </c>
       <c r="D2" t="n">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>21.3%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp1.600.000</t>
+          <t>Rp1.840.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -730,16 +730,16 @@
         <v>72</v>
       </c>
       <c r="D10" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp6.035.989</t>
+          <t>Rp5.697.989</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -854,16 +854,16 @@
         <v>180</v>
       </c>
       <c r="D14" t="n">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>21.1%</t>
+          <t>20.6%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp9.045.000</t>
+          <t>Rp8.715.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -978,16 +978,16 @@
         <v>72</v>
       </c>
       <c r="D18" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>23.6%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp2.700.000</t>
+          <t>Rp2.800.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1009,16 +1009,16 @@
         <v>108</v>
       </c>
       <c r="D19" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>20.4%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp3.520.000</t>
+          <t>Rp3.620.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1226,16 +1226,16 @@
         <v>68</v>
       </c>
       <c r="D26" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp575.000</t>
+          <t>Rp700.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1350,16 +1350,16 @@
         <v>54</v>
       </c>
       <c r="D30" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp2.400.000</t>
+          <t>Rp2.880.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1505,16 +1505,16 @@
         <v>72</v>
       </c>
       <c r="D35" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp2.640.000</t>
+          <t>Rp2.836.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -1567,16 +1567,16 @@
         <v>72</v>
       </c>
       <c r="D37" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>51.4%</t>
+          <t>48.6%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp5.600.000</t>
+          <t>Rp5.350.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -1691,16 +1691,16 @@
         <v>54</v>
       </c>
       <c r="D41" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp1.125.000</t>
+          <t>Rp1.320.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -1784,16 +1784,16 @@
         <v>198</v>
       </c>
       <c r="D44" t="n">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>14.1%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp4.025.000</t>
+          <t>Rp4.175.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2280,16 +2280,16 @@
         <v>36</v>
       </c>
       <c r="D60" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rp149.000</t>
+          <t>Rp248.000</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -2497,16 +2497,16 @@
         <v>90</v>
       </c>
       <c r="D67" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rp3.328.000</t>
+          <t>Rp3.726.000</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -2869,16 +2869,16 @@
         <v>108</v>
       </c>
       <c r="D79" t="n">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>28.7%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Rp2.975.000</t>
+          <t>Rp3.350.000</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -3427,16 +3427,16 @@
         <v>112</v>
       </c>
       <c r="D97" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>33.9%</t>
+          <t>34.8%</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Rp6.370.000</t>
+          <t>Rp6.610.000</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -3602,16 +3602,16 @@
         <v>127</v>
       </c>
       <c r="D3" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>57.5%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp17.284.000</t>
+          <t>Rp17.569.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -3664,16 +3664,16 @@
         <v>96</v>
       </c>
       <c r="D5" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp13.300.000</t>
+          <t>Rp14.350.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -3912,16 +3912,16 @@
         <v>57</v>
       </c>
       <c r="D13" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>24.6%</t>
+          <t>28.1%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp5.050.000</t>
+          <t>Rp5.450.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -4191,16 +4191,16 @@
         <v>34</v>
       </c>
       <c r="D22" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>55.9%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp3.300.000</t>
+          <t>Rp3.495.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -4532,16 +4532,16 @@
         <v>90</v>
       </c>
       <c r="D33" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>18.9%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp2.925.000</t>
+          <t>Rp3.225.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4718,16 +4718,16 @@
         <v>32</v>
       </c>
       <c r="D39" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp4.700.000</t>
+          <t>Rp5.000.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -5183,16 +5183,16 @@
         <v>68</v>
       </c>
       <c r="D54" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>39.7%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rp7.975.000</t>
+          <t>Rp8.305.000</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -5854,16 +5854,16 @@
         <v>108</v>
       </c>
       <c r="D5" t="n">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp9.800.000</t>
+          <t>Rp10.800.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -5885,16 +5885,16 @@
         <v>36</v>
       </c>
       <c r="D6" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp2.475.000</t>
+          <t>Rp2.675.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -5947,16 +5947,16 @@
         <v>272</v>
       </c>
       <c r="D8" t="n">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>27.6%</t>
+          <t>28.3%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp36.550.000</t>
+          <t>Rp37.750.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -6009,16 +6009,16 @@
         <v>72</v>
       </c>
       <c r="D10" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>40.3%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp7.285.000</t>
+          <t>Rp6.785.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -6133,16 +6133,16 @@
         <v>51</v>
       </c>
       <c r="D14" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp4.225.000</t>
+          <t>Rp4.400.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6432,16 +6432,16 @@
         <v>101</v>
       </c>
       <c r="D3" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>14.9%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp11.450.000</t>
+          <t>Rp11.200.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -6494,16 +6494,16 @@
         <v>90</v>
       </c>
       <c r="D5" t="n">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp666.000</t>
+          <t>Rp1.122.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6556,16 +6556,16 @@
         <v>144</v>
       </c>
       <c r="D7" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>21.5%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp9.625.000</t>
+          <t>Rp9.800.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -7052,16 +7052,16 @@
         <v>112</v>
       </c>
       <c r="D23" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>36.6%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp8.210.000</t>
+          <t>Rp8.410.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -7176,16 +7176,16 @@
         <v>96</v>
       </c>
       <c r="D27" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>40.6%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp8.050.000</t>
+          <t>Rp8.300.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -7371,7 +7371,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp16.250.000</t>
+          <t>Rp16.700.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -7424,16 +7424,16 @@
         <v>102</v>
       </c>
       <c r="D35" t="n">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp1.637.000</t>
+          <t>Rp2.234.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -7548,16 +7548,16 @@
         <v>150</v>
       </c>
       <c r="D39" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>62.0%</t>
+          <t>62.7%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp28.700.000</t>
+          <t>Rp28.900.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -7858,16 +7858,16 @@
         <v>144</v>
       </c>
       <c r="D49" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>15.3%</t>
+          <t>16.0%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp3.650.000</t>
+          <t>Rp3.825.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -8436,16 +8436,16 @@
         <v>54</v>
       </c>
       <c r="D17" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp1.089.000</t>
+          <t>Rp1.188.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -8498,16 +8498,16 @@
         <v>54</v>
       </c>
       <c r="D19" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp2.090.000</t>
+          <t>Rp2.260.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8870,16 +8870,16 @@
         <v>54</v>
       </c>
       <c r="D31" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp3.075.000</t>
+          <t>Rp3.375.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -9087,16 +9087,16 @@
         <v>72</v>
       </c>
       <c r="D38" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>59.7%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp3.470.000</t>
+          <t>Rp3.767.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -9211,16 +9211,16 @@
         <v>68</v>
       </c>
       <c r="D42" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>20.6%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp1.993.000</t>
+          <t>Rp2.233.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
